--- a/product_selector_out/STM32G0x0 value line.xlsx
+++ b/product_selector_out/STM32G0x0 value line.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10109,9 +10109,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10174,14 +10174,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -10339,9 +10339,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10409,9 +10409,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11417,9 +11417,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11482,14 +11482,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -11647,9 +11647,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -11717,9 +11717,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11744,9 +11744,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -11809,14 +11809,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -11974,9 +11974,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -12044,9 +12044,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13373,7 +13373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13935,7 +13935,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13950,14 +13950,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13972,14 +13972,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13994,14 +13994,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -14016,14 +14016,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -14038,14 +14038,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -14060,14 +14060,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14082,14 +14082,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14104,14 +14104,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14126,14 +14126,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -14155,7 +14155,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14177,7 +14177,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -14199,7 +14199,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14214,14 +14214,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -14236,14 +14236,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14258,14 +14258,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14280,14 +14280,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14302,14 +14302,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14324,14 +14324,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14353,7 +14353,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14375,7 +14375,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -14389,204 +14389,6 @@
         </is>
       </c>
       <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32G050K8</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32G050K8</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32G050K8</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0x0 value line.xlsx
+++ b/product_selector_out/STM32G0x0 value line.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -10109,9 +10109,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -10174,14 +10174,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -10339,9 +10339,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AY20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10409,9 +10409,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11417,9 +11417,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11482,14 +11482,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -11647,9 +11647,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AY24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -11717,9 +11717,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11744,9 +11744,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -11809,14 +11809,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -11974,9 +11974,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AY25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -12044,9 +12044,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13373,7 +13373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13935,7 +13935,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13950,14 +13950,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13972,14 +13972,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13994,14 +13994,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -14016,14 +14016,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -14038,14 +14038,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -14060,14 +14060,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14082,14 +14082,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14104,14 +14104,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14126,14 +14126,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -14155,7 +14155,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14177,7 +14177,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -14199,7 +14199,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G0B0RE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14214,14 +14214,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G0B0RE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -14236,14 +14236,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G0B0RE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14258,14 +14258,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G0B0VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14280,14 +14280,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G0B0VE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14302,14 +14302,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G050K6</t>
+          <t>STM32G0B0VE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14324,14 +14324,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32G050F6</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14353,7 +14353,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G050F6</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14375,20 +14375,218 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>STM32G050C6</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32G050K8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32G050K6</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>STM32G050F6</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32G050F6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32G050F6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0x0 value line.xlsx
+++ b/product_selector_out/STM32G0x0 value line.xlsx
@@ -2622,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g070cb.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g070cb.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8801,9 +8801,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8866,14 +8866,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -9031,9 +9031,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ16" s="8" t="inlineStr">
@@ -9101,9 +9101,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9782,9 +9782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -9847,14 +9847,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -10012,9 +10012,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AY19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AY19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ19" s="8" t="inlineStr">
@@ -10082,9 +10082,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13373,7 +13373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13671,7 +13671,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13686,14 +13686,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13708,14 +13708,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32G070RB</t>
+          <t>STM32G030K8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -13730,14 +13730,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -13759,7 +13759,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -13781,7 +13781,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32G030K8</t>
+          <t>STM32G030K6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -13803,7 +13803,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -13818,14 +13818,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13840,14 +13840,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32G030K6</t>
+          <t>STM32G0B0KE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13862,14 +13862,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13884,14 +13884,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13906,14 +13906,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32G070KB</t>
+          <t>STM32G030C8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13928,14 +13928,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 24. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13957,7 +13957,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13979,7 +13979,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32G0B0KE</t>
+          <t>STM32G0B0CE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -14001,7 +14001,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -14023,7 +14023,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -14045,7 +14045,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G030C8</t>
+          <t>STM32G030C6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -14067,7 +14067,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G0B0RE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14089,7 +14089,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G0B0RE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14111,7 +14111,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32G0B0CE</t>
+          <t>STM32G0B0RE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14133,7 +14133,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G0B0VE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -14148,14 +14148,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G0B0VE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14170,14 +14170,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G030C6</t>
+          <t>STM32G0B0VE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -14192,14 +14192,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14214,14 +14214,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -14236,14 +14236,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32G0B0RE</t>
+          <t>STM32G050C6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14258,14 +14258,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14280,14 +14280,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14302,14 +14302,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G0B0VE</t>
+          <t>STM32G050K8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14324,14 +14324,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14353,7 +14353,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14375,7 +14375,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G050C6</t>
+          <t>STM32G050K6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -14397,7 +14397,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -14419,7 +14419,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14441,7 +14441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G050K8</t>
+          <t>STM32G050F6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -14455,138 +14455,6 @@
         </is>
       </c>
       <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32G050K6</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32G050F6</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0x0 value line.xlsx
+++ b/product_selector_out/STM32G0x0 value line.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.70703125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g070cb.pdf</t>
         </is>
       </c>
@@ -2625,6 +2652,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -3606,6 +3648,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g030c6.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
@@ -6873,12 +6965,17 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g050c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6899,16 +6996,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6921,6 +7016,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6940,7 +7036,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6975,7 +7073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7043,6 +7141,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7376,6 +7475,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7471,6 +7575,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7793,7 +7898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8120,7 +8230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8447,7 +8562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8774,7 +8894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9106,6 +9231,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9428,7 +9558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9755,7 +9890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10087,6 +10227,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -10409,7 +10554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10736,7 +10886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11063,7 +11218,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11390,7 +11550,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11717,7 +11882,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12044,7 +12214,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12371,7 +12546,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12698,7 +12878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13025,7 +13210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13352,7 +13542,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13360,8 +13555,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
